--- a/locations.xlsx
+++ b/locations.xlsx
@@ -1096,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Itanagar</t>
+          <t>Tirupati</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Naharlagun</t>
+          <t>Kurnool</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Guwahati</t>
+          <t>Nellore</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dibrugarh</t>
+          <t>Rajahmundry</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Silchar</t>
+          <t>Itanagar</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Naharlagun</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gaya</t>
+          <t>Tawang</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Muzaffarpur</t>
+          <t>Pasighat</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Guwahati</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bilaspur</t>
+          <t>Dibrugarh</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durg</t>
+          <t>Silchar</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Panaji</t>
+          <t>Jorhat</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Margao</t>
+          <t>Tezpur</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patna</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GJ</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Gaya</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GJ</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Muzaffarpur</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GJ</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Bhagalpur</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GJ</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Darbhanga</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Raipur</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faridabad</t>
+          <t>Bilaspur</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Panipat</t>
+          <t>Durg</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shimla</t>
+          <t>Korba</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dharamshala</t>
+          <t>Jagdalpur</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Solan</t>
+          <t>Panaji</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Margao</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Mapusa</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dhanbad</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Surat</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Vadodara</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Rajkot</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Bhavnagar</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Gurugram</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kozhikode</t>
+          <t>Faridabad</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Panipat</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Ambala</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jabalpur</t>
+          <t>Hisar</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gwalior</t>
+          <t>Shimla</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dharamshala</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Solan</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mandi</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Ranchi</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Aurangabad</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kolhapur</t>
+          <t>Dhanbad</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Solapur</t>
+          <t>Bokaro</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Imphal</t>
+          <t>Mysuru</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shillong</t>
+          <t>Mangaluru</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tura</t>
+          <t>Hubballi</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aizawl</t>
+          <t>Belagavi</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lunglei</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kohima</t>
+          <t>Kochi</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dimapur</t>
+          <t>Kozhikode</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OD</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Thrissur</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OD</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cuttack</t>
+          <t>Bhopal</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OD</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Indore</t>
         </is>
       </c>
     </row>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
+          <t>Gwalior</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Jabalpur</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jalandhar</t>
+          <t>Ujjain</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Pune</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Nagpur</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kota</t>
+          <t>Nashik</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Thane</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Namchi</t>
+          <t>Aurangabad</t>
         </is>
       </c>
     </row>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Imphal</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Thoubal</t>
         </is>
       </c>
     </row>
@@ -2314,12 +2314,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Bishnupur</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salem</t>
+          <t>Shillong</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tiruchirappalli</t>
+          <t>Tura</t>
         </is>
       </c>
     </row>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Jowai</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>MZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Aizawl</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>MZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Karimnagar</t>
+          <t>Lunglei</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>MZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Agartala</t>
+          <t>Champhai</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Kohima</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Dimapur</t>
         </is>
       </c>
     </row>
@@ -2467,12 +2467,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Mokokchung</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>OD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>OD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prayagraj</t>
+          <t>Cuttack</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>OD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>Rourkela</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>OD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Sambalpur</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Haridwar</t>
+          <t>Ludhiana</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2569,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Haldwani</t>
+          <t>Amritsar</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Jalandhar</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Patiala</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Durgapur</t>
+          <t>Jaipur</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Siliguri</t>
+          <t>Jodhpur</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Port Blair</t>
+          <t>Udaipur</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Kota</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Daman</t>
+          <t>Ajmer</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Silvassa</t>
+          <t>Gangtok</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Namchi</t>
         </is>
       </c>
     </row>
@@ -2739,12 +2739,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gyalshing</t>
         </is>
       </c>
     </row>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JK</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Chennai</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JK</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jammu</t>
+          <t>Coimbatore</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Leh</t>
+          <t>Madurai</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kargil</t>
+          <t>Salem</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LD</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kavaratti</t>
+          <t>Tiruchirappalli</t>
         </is>
       </c>
     </row>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Hyderabad</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2858,590 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Agartala</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Dharmanagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Varanasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Prayagraj</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Dehradun</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Haridwar</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Haldwani</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Roorkee</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Durgapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Siliguri</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Asansol</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Port Blair</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Leh</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Kargil</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Kavaratti</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>PY</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PY</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>Karaikal</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PY</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mahe</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PY</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Yanam</t>
         </is>
       </c>
     </row>

--- a/locations.xlsx
+++ b/locations.xlsx
@@ -19,13 +19,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,8 +55,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1096,2352 +1108,7027 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Country ISO</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>State Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Visakhapatnam</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Vijayawada</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Guntur</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Nellore</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Rajahmundry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Tirupati</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Kurnool</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kadapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nellore</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Kakinada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Rajahmundry</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Anantapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Eluru</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Ongole</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Chittoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Srikakulam</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Machilipatnam</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Tenali</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Proddatur</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Adoni</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Vizianagaram</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Nandyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Itanagar</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Naharlagun</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Tawang</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Pasighat</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Ziro</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Bomdila</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Along</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Tezu</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Changlang</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Khonsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Guwahati</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Dibrugarh</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Silchar</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Jorhat</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Tezpur</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Sivasagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Bongaigaon</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Karimganj</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Goalpara</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Dhubri</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>North Lakhimpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Diphu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Golaghat</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Patna</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Gaya</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Muzaffarpur</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Bhagalpur</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Darbhanga</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Purnia</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Ara</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Begusarai</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Katihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Munger</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Chhapra</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Bettiah</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Saharsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Sasaram</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Hajipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Siwan</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Motihari</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Bihar Sharif</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Raipur</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Bilaspur</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Durg</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Korba</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Jagdalpur</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Rajnandgaon</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Ambikapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Raigarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Dhamtari</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Bhilai</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Chirmiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Kanker</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Panaji</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Margao</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Mapusa</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Vasco da Gama</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Ponda</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Bicholim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Curchorem</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Sanguem</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Canacona</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Valpoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>GJ</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Ahmedabad</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>GJ</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Surat</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>GJ</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Vadodara</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>GJ</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Rajkot</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>GJ</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Bhavnagar</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Jamnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Junagadh</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Gandhinagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Anand</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Nadiad</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Morbi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Mehsana</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Bharuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Porbandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Navsari</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Valsad</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Palanpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Godhra</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Patan</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Veraval</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>Faridabad</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>Panipat</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>Ambala</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>Hisar</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Rohtak</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Karnal</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Sonipat</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Yamunanagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Panchkula</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Bhiwani</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Sirsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Rewari</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Kurukshetra</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Jind</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Kaithal</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>Shimla</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>Dharamshala</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>Solan</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Mandi</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Kullu</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Manali</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Una</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Hamirpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Chamba</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Nahan</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Palampur</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Kasauli</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>Ranchi</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>Jamshedpur</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>Dhanbad</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>Bokaro</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Deoghar</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Hazaribagh</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Giridih</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Ramgarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Medininagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Chaibasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Dumka</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Phusro</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>Mysuru</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Hubballi</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>Mangaluru</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Hubballi</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Belagavi</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Kalaburagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Davanagere</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Ballari</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Shivamogga</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Tumakuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Udupi</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Bidar</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Hassan</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Gadag</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Chikkamagaluru</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Bagalkot</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Raichur</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Kolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>KL</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>Thiruvananthapuram</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>KL</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>Kochi</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>KL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>Kozhikode</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t>KL</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Kollam</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>Thrissur</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Alappuzha</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Palakkad</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Kottayam</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Malappuram</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Kasaragod</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Pathanamthitta</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Idukki</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Wayanad</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>Bhopal</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>Indore</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t>Gwalior</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t>Jabalpur</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t>Ujjain</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Sagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Dewas</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Satna</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Ratlam</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Rewa</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Murwara</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Singrauli</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Burhanpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Khandwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Bhind</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Chhindwara</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Vidisha</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Shivpuri</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Damoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>Nagpur</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>Nashik</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>Thane</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>Aurangabad</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Amravati</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Akola</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Dhule</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Ahmednagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Chandrapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Nanded</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Wardha</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C220" s="3" t="inlineStr">
         <is>
           <t>Imphal</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C221" s="3" t="inlineStr">
         <is>
           <t>Thoubal</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C222" s="3" t="inlineStr">
         <is>
           <t>Bishnupur</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Churachandpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Kakching</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Ukhrul</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Senapati</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Jiribam</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C228" s="3" t="inlineStr">
         <is>
           <t>Shillong</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C229" s="3" t="inlineStr">
         <is>
           <t>Tura</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C230" s="3" t="inlineStr">
         <is>
           <t>Jowai</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Nongstoin</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Baghmara</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Williamnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>Resubelpara</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C235" s="3" t="inlineStr">
         <is>
           <t>Aizawl</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C236" s="3" t="inlineStr">
         <is>
           <t>Lunglei</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C237" s="3" t="inlineStr">
         <is>
           <t>Champhai</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Serchhip</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Kolasib</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Saiha</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Mamit</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C242" s="3" t="inlineStr">
         <is>
           <t>Kohima</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C243" s="3" t="inlineStr">
         <is>
           <t>Dimapur</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C244" s="3" t="inlineStr">
         <is>
           <t>Mokokchung</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Tuensang</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Wokha</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Zunheboto</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Phek</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C250" s="3" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C251" s="3" t="inlineStr">
         <is>
           <t>Cuttack</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C252" s="3" t="inlineStr">
         <is>
           <t>Rourkela</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Berhampur</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
         <is>
           <t>Sambalpur</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>Puri</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Balasore</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Baripada</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Bhadrak</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Jharsuguda</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Angul</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Jeypore</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C262" s="3" t="inlineStr">
         <is>
           <t>Ludhiana</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C263" s="3" t="inlineStr">
         <is>
           <t>Amritsar</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C264" s="3" t="inlineStr">
         <is>
           <t>Jalandhar</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C265" s="3" t="inlineStr">
         <is>
           <t>Patiala</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Bathinda</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Pathankot</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Hoshiarpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Batala</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Moga</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Firozpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Kapurthala</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Sangrur</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Barnala</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C276" s="3" t="inlineStr">
         <is>
           <t>Jaipur</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C277" s="3" t="inlineStr">
         <is>
           <t>Jodhpur</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C278" s="3" t="inlineStr">
         <is>
           <t>Udaipur</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C279" s="3" t="inlineStr">
         <is>
           <t>Kota</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Bikaner</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
         <is>
           <t>Ajmer</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Bhilwara</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Alwar</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>Sikar</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Bharatpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>Pali</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>Sri Ganganagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Kishangarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Baran</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Churu</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Jhunjhunu</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Nagaur</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Tonk</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C294" s="3" t="inlineStr">
         <is>
           <t>Gangtok</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C295" s="3" t="inlineStr">
         <is>
           <t>Namchi</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C296" s="3" t="inlineStr">
         <is>
           <t>Gyalshing</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Mangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>Rangpo</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>Jorethang</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C300" s="3" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C301" s="3" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C302" s="3" t="inlineStr">
         <is>
           <t>Madurai</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
         <is>
           <t>Salem</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Tiruchirappalli</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>Tirunelveli</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>Vellore</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>Thoothukudi</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>Dindigul</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>Thanjavur</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>Nagercoil</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>Kanchipuram</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>Karur</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>Cuddalore</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
         <is>
           <t>TS</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C316" s="3" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
         <is>
           <t>TS</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C317" s="3" t="inlineStr">
         <is>
           <t>Warangal</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
         <is>
           <t>TS</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C318" s="3" t="inlineStr">
         <is>
           <t>Nizamabad</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
         <is>
           <t>TS</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C319" s="3" t="inlineStr">
         <is>
           <t>Karimnagar</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>Ramagundam</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>Miryalaguda</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C328" s="3" t="inlineStr">
         <is>
           <t>Agartala</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C329" s="3" t="inlineStr">
         <is>
           <t>Udaipur</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C330" s="3" t="inlineStr">
         <is>
           <t>Dharmanagar</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>Kailashahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>Belonia</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>Khowai</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>Ambassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C335" s="3" t="inlineStr">
         <is>
           <t>Lucknow</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C336" s="3" t="inlineStr">
         <is>
           <t>Kanpur</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
         <is>
           <t>Varanasi</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Agra</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>Meerut</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C341" s="3" t="inlineStr">
         <is>
           <t>Prayagraj</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>Bareilly</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>Aligarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>Saharanpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>Gorakhpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
         <is>
           <t>Noida</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ghaziabad</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>Firozabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>Jhansi</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>Muzaffarnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>Mathura</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="inlineStr">
+        <is>
+          <t>Rampur</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>Shahjahanpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C354" s="3" t="inlineStr">
+        <is>
+          <t>Farrukhabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C355" s="3" t="inlineStr">
         <is>
           <t>Dehradun</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C356" s="3" t="inlineStr">
         <is>
           <t>Haridwar</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>Roorkee</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
         <is>
           <t>Haldwani</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Roorkee</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
+      <c r="C359" s="3" t="inlineStr">
+        <is>
+          <t>Rudrapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C360" s="3" t="inlineStr">
+        <is>
+          <t>Kashipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="inlineStr">
+        <is>
+          <t>Rishikesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C362" s="3" t="inlineStr">
+        <is>
+          <t>Nainital</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>Almora</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C364" s="3" t="inlineStr">
+        <is>
+          <t>Pithoragarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>Pauri</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C366" s="3" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C367" s="3" t="inlineStr">
         <is>
           <t>Howrah</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C368" s="3" t="inlineStr">
         <is>
           <t>Durgapur</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
+    <row r="369">
+      <c r="A369" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C369" s="3" t="inlineStr">
+        <is>
+          <t>Asansol</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C370" s="3" t="inlineStr">
         <is>
           <t>Siliguri</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
+    <row r="371">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Asansol</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
+      <c r="C371" s="3" t="inlineStr">
+        <is>
+          <t>Bardhaman</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="inlineStr">
+        <is>
+          <t>Malda</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>Baharampur</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C374" s="3" t="inlineStr">
+        <is>
+          <t>Habra</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C375" s="3" t="inlineStr">
+        <is>
+          <t>Kharagpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C376" s="3" t="inlineStr">
+        <is>
+          <t>Krishnanagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C377" s="3" t="inlineStr">
+        <is>
+          <t>Darjeeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C378" s="3" t="inlineStr">
+        <is>
+          <t>Jalpaiguri</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>Cooch Behar</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
         <is>
           <t>AN</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C380" s="3" t="inlineStr">
         <is>
           <t>Port Blair</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
+    <row r="381">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="inlineStr">
+        <is>
+          <t>Diglipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="C382" s="3" t="inlineStr">
+        <is>
+          <t>Rangat</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="inlineStr">
+        <is>
+          <t>Mayabunder</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="C384" s="3" t="inlineStr">
+        <is>
+          <t>Car Nicobar</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C385" s="3" t="inlineStr">
         <is>
           <t>Chandigarh</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="C386" s="3" t="inlineStr">
+        <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="inlineStr">
+        <is>
+          <t>Daman</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="inlineStr">
+        <is>
+          <t>Diu</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
         <is>
           <t>DL</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C389" s="3" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
+    <row r="390">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
         <is>
           <t>DL</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
+      <c r="C390" s="3" t="inlineStr">
+        <is>
+          <t>Delhi Cantonment</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="inlineStr">
+        <is>
+          <t>Rohini</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C393" s="3" t="inlineStr">
+        <is>
+          <t>Narela</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
         <is>
           <t>JK</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C394" s="3" t="inlineStr">
         <is>
           <t>Srinagar</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
+    <row r="395">
+      <c r="A395" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
         <is>
           <t>JK</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C395" s="3" t="inlineStr">
         <is>
           <t>Jammu</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
+    <row r="396">
+      <c r="A396" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C396" s="3" t="inlineStr">
+        <is>
+          <t>Anantnag</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C397" s="3" t="inlineStr">
+        <is>
+          <t>Baramulla</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C398" s="3" t="inlineStr">
+        <is>
+          <t>Sopore</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>Udhampur</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C400" s="3" t="inlineStr">
+        <is>
+          <t>Kathua</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C401" s="3" t="inlineStr">
+        <is>
+          <t>Rajouri</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C402" s="3" t="inlineStr">
+        <is>
+          <t>Poonch</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>JK</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="inlineStr">
+        <is>
+          <t>Kupwara</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
         <is>
           <t>LA</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C404" s="3" t="inlineStr">
         <is>
           <t>Leh</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
         <is>
           <t>LA</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C405" s="3" t="inlineStr">
         <is>
           <t>Kargil</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
         <is>
           <t>LD</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C406" s="3" t="inlineStr">
         <is>
           <t>Kavaratti</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
+    <row r="407">
+      <c r="A407" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="inlineStr">
+        <is>
+          <t>Agatti</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="inlineStr">
+        <is>
+          <t>Amini</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="inlineStr">
+        <is>
+          <t>Andrott</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
         <is>
           <t>PY</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C410" s="3" t="inlineStr">
         <is>
           <t>Puducherry</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
+    <row r="411">
+      <c r="A411" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
         <is>
           <t>PY</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C411" s="3" t="inlineStr">
         <is>
           <t>Karaikal</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
+    <row r="412">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
         <is>
           <t>PY</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C412" s="3" t="inlineStr">
+        <is>
+          <t>Yanam</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>PY</t>
+        </is>
+      </c>
+      <c r="C413" s="3" t="inlineStr">
         <is>
           <t>Mahe</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>PY</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Yanam</t>
         </is>
       </c>
     </row>
